--- a/مثال_إحصائية_الموظفين_الغائبين.xlsx
+++ b/مثال_إحصائية_الموظفين_الغائبين.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="49">
   <si>
     <t xml:space="preserve">المملكة العربية السعودية
 وزارة التعليم
@@ -111,13 +111,16 @@
     <t>حسم</t>
   </si>
   <si>
+    <t>نعم</t>
+  </si>
+  <si>
+    <t>1448/04/04</t>
+  </si>
+  <si>
     <t>لا</t>
   </si>
   <si>
-    <t>غياب بدون عذر</t>
-  </si>
-  <si>
-    <t>1448/04/04</t>
+    <t>لم يصدر قرار الحسم بعد</t>
   </si>
   <si>
     <t>سالم حسن</t>
@@ -132,9 +135,6 @@
     <t>مساءلة غياب</t>
   </si>
   <si>
-    <t>نعم</t>
-  </si>
-  <si>
     <t>مراجعة مستشفى</t>
   </si>
   <si>
@@ -160,6 +160,9 @@
   </si>
   <si>
     <t>1033333333</t>
+  </si>
+  <si>
+    <t>حسم تأخر</t>
   </si>
   <si>
     <t>تأخر — يوم واحد حسم</t>
@@ -818,7 +821,7 @@
         <v>26</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="M4" s="5" t="s">
         <v>18</v>
@@ -856,16 +859,16 @@
         <v>23</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J5" s="5" t="s">
         <v>25</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="M5" s="5" t="s">
         <v>18</v>
@@ -897,22 +900,22 @@
         <v>21</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="L6" s="5" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="M6" s="5" t="s">
         <v>18</v>
@@ -921,7 +924,7 @@
         <v>18</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -953,10 +956,10 @@
         <v>37</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L7" s="5" t="s">
         <v>38</v>
@@ -991,10 +994,10 @@
         <v>21</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I8" s="5" t="s">
         <v>39</v>
@@ -1003,7 +1006,7 @@
         <v>25</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L8" s="5" t="s">
         <v>40</v>
@@ -1047,10 +1050,10 @@
         <v>18</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="L9" s="5" t="s">
         <v>18</v>
@@ -1062,7 +1065,7 @@
         <v>26</v>
       </c>
       <c r="O9" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -1073,7 +1076,7 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -1085,7 +1088,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
@@ -1097,7 +1100,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
@@ -1109,7 +1112,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
